--- a/docs/data/lexi-bridge-ff4-v2/法语专四假朋友题库_V3.xlsx
+++ b/docs/data/lexi-bridge-ff4-v2/法语专四假朋友题库_V3.xlsx
@@ -547,7 +547,7 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>229</v>
+        <v>239</v>
       </c>
     </row>
     <row r="8">
@@ -567,7 +567,7 @@
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10">
@@ -577,7 +577,7 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
     </row>
     <row r="11">
@@ -646,7 +646,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>严格执行 0811 文档模板，答案全部为 F，不另造控制题。</t>
+          <t>按客户反馈加入 10 道英法同形同义 Vrai 控制题，并在假朋友 F 题中确定性穿插。</t>
         </is>
       </c>
     </row>
@@ -1055,116 +1055,45 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>LEXI_BRIDGE_FF4-0286</t>
+          <t>LEXI_BRIDGE_FF4-0038</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>coin</t>
+          <t>complémentaire</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>coin</t>
+          <t>complémentaire</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>怜悯</t>
+          <t>大胆的; 放肆的、厚脸皮的</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>担保; 保证</t>
+          <t>有规律的</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>硬币</t>
+          <t>补充的；互补的</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>角落、隅；一小块、一隅之地</t>
+          <t>赞美的</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>法语词：coin；易混英文词：coin。
-TEM4 前 2–3 义项：角落、隅；一小块、一隅之地。
-英文迁移义：硬币。
-来源：TEM4 p.223；假朋友词典 p.39。
-生产审查：APPROVED（核心义完全不重合、词性、选项角色与答案一致性已复核）。</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>TEM4 p.223；假朋友词典 p.39</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>APPROVED</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>APPROVED</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>FF4PROD-T1-006</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>LEXI_BRIDGE_FF4-0038</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>complémentaire</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>complémentaire</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>贵重的; 宝贵的</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>补充的；互补的</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>暗的; 阴郁的</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>赞美的</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
         <is>
           <t>法语词：complémentaire；易混英文词：complimentary。
 TEM4 前 2–3 义项：补充的；互补的。
@@ -1173,140 +1102,69 @@
 生产审查：APPROVED（核心义完全不重合、词性、选项角色与答案一致性已复核）。</t>
         </is>
       </c>
-      <c r="K9" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>TEM4 p.41；假朋友词典 p.41</t>
         </is>
       </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>APPROVED</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>APPROVED</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>FF4PROD-T1-007</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>LEXI_BRIDGE_FF4-0233</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>convenir</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>convenir</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>使转向; 拍摄（影视）</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>召集</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>刺; 扎</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>适合、使中意；约定；适合的</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>法语词：convenir；易混英文词：convene。
-TEM4 前 2–3 义项：适合、使中意；约定；适合的。
-英文迁移义：召集。
-来源：TEM4 p.177；假朋友词典 p.47。
-生产审查：APPROVED（核心义完全不重合、词性、选项角色与答案一致性已复核）。</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>TEM4 p.177；假朋友词典 p.47</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>APPROVED</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>APPROVED</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>FF4PROD-T1-008</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>FF4PROD-T1-006</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>LEXI_BRIDGE_FF4-0041</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>disposer</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>disposer</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>走; 运行</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>改革</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>处理；处置</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr">
         <is>
           <t>摆放；拥有；准备</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>安顿; 安家</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>指挥; 命令某人做某事</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
         <is>
           <t>法语词：disposer；易混英文词：dispose。
 TEM4 前 2–3 义项：摆放；拥有；准备。
@@ -1315,140 +1173,69 @@
 生产审查：APPROVED（核心义完全不重合、词性、选项角色与答案一致性已复核）。</t>
         </is>
       </c>
-      <c r="K11" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>TEM4 p.42；假朋友词典 p.65</t>
         </is>
       </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>APPROVED</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>APPROVED</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>FF4PROD-T1-009</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>LEXI_BRIDGE_FF4-0327</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>don</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>don</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>金额、款项; 总量</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>喧哗; 谣传</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>捐赠；天赋</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>先生</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>法语词：don；易混英文词：don。
-TEM4 前 2–3 义项：捐赠；天赋。
-英文迁移义：先生。
-来源：TEM4 p.256；假朋友词典 p.66。
-生产审查：APPROVED（核心义完全不重合、词性、选项角色与答案一致性已复核）。</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>TEM4 p.256；假朋友词典 p.66</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>APPROVED</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>APPROVED</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>FF4PROD-T1-010</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>FF4PROD-T1-007</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>LEXI_BRIDGE_FF4-0386</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>doter</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>doter</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>待、停留; 保持</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>集合; 归队</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>装备；配备；授予</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>溺爱</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>装备；配备；授予</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>吸（气）; 使获得灵感</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>解开; 使移开</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>法语词：doter；易混英文词：dote。
 TEM4 前 2–3 义项：装备；配备；授予。
@@ -1457,141 +1244,69 @@
 生产审查：APPROVED（核心义完全不重合、词性、选项角色与答案一致性已复核）。</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>TEM4 p.312；假朋友词典 p.66</t>
         </is>
       </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>APPROVED</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>APPROVED</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>FF4PROD-T1-011</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>LEXI_BRIDGE_FF4-0304</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>désigner</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>désigner</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>设计</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>估价; 估计</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>指、指出；意思是；指定</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>再上; 重新登上</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>法语词：désigner；易混英文词：design。
-TEM4 前 2–3 义项：指、指出；意思是；指定。
-英文迁移义：设计。
-来源：TEM4 p.242；假朋友词典 p.61。
-生产审查：APPROVED（核心义完全不重合、词性、选项角色与答案一致性已复核）。
-迁移干扰（原书证据）：dessiner —— …To design = dessiner, créer. désister Oc。</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>TEM4 p.242；假朋友词典 p.61</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>APPROVED</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>APPROVED</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>FF4PROD-T1-012</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>FF4PROD-T1-008</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>LEXI_BRIDGE_FF4-0030</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
         <is>
           <t>entraîner</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>entraîner</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>卷走；拖；拉</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>领入、引荐; 引进</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>碰撞; 触犯</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>兴致</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>卷走；拖；拉</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>推动; 行驶</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>接替; 继而来</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
         <is>
           <t>法语词：entraîner；易混英文词：entrain。
 TEM4 前 2–3 义项：卷走；拖；拉。
@@ -1600,69 +1315,69 @@
 生产审查：APPROVED（核心义完全不重合、词性、选项角色与答案一致性已复核）。</t>
         </is>
       </c>
-      <c r="K15" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>TEM4 p.34；假朋友词典 p.73</t>
         </is>
       </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>APPROVED</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>APPROVED</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>FF4PROD-T1-013</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>FF4PROD-T1-009</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>LEXI_BRIDGE_FF4-0316</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>fin</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>fin</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>大的; 高的</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>细的、薄的；精美的；敏锐的</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>可能的</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>鳍；金融</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>补充的; 互补的</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>健康的</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
         <is>
           <t>法语词：fin；易混英文词：fin。
 TEM4 前 2–3 义项：细的、薄的；精美的；敏锐的。
@@ -1671,69 +1386,69 @@
 生产审查：APPROVED（核心义完全不重合、词性、选项角色与答案一致性已复核）。</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>TEM4 p.250；假朋友词典 p.81</t>
         </is>
       </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>APPROVED</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>APPROVED</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>FF4PROD-T1-014</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>FF4PROD-T1-010</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>LEXI_BRIDGE_FF4-0261</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
         <is>
           <t>fondre</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>fondre</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>失败；沉没</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
         <is>
           <t>使融化、使熔格化；使合并；融化、熔化</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>失败；沉没</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>请求; 申请</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>使着迷; 吸引</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>促使</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>压榨、挤、按; 催促</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>法语词：fondre；易混英文词：founder。
 TEM4 前 2–3 义项：使融化、使熔格化；使合并；融化、熔化。
@@ -1742,69 +1457,69 @@
 生产审查：APPROVED（核心义完全不重合、词性、选项角色与答案一致性已复核）。</t>
         </is>
       </c>
-      <c r="K17" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>TEM4 p.200；假朋友词典 p.83</t>
         </is>
       </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>APPROVED</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>APPROVED</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>FF4PROD-T1-015</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>FF4PROD-T1-011</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>LEXI_BRIDGE_FF4-0179</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
         <is>
           <t>former</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>former</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>奉承</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>制作、形成、使成形；组建；构成</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>强行弄开; 强迫</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>以前的</t>
         </is>
       </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>扣留、扣除; 预定</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>要求; 请求</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
         <is>
           <t>法语词：former；易混英文词：former。
 TEM4 前 2–3 义项：制作、形成、使成形；组建；构成。
@@ -1813,69 +1528,69 @@
 生产审查：APPROVED（核心义完全不重合、词性、选项角色与答案一致性已复核）。</t>
         </is>
       </c>
-      <c r="K18" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>TEM4 p.139；假朋友词典 p.85</t>
         </is>
       </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>APPROVED</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>APPROVED</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>FF4PROD-T1-016</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>FF4PROD-T1-012</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>LEXI_BRIDGE_FF4-0037</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
         <is>
           <t>four</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>four</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>流感</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>讲台; 主席台</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>烤炉；烤箱</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
         <is>
           <t>四</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>直行; 直列</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>烤炉；烤箱</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>水库; （盛液体或气体的）容器</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
         <is>
           <t>法语词：four；易混英文词：four。
 TEM4 前 2–3 义项：烤炉；烤箱。
@@ -1884,69 +1599,69 @@
 生产审查：APPROVED（核心义完全不重合、词性、选项角色与答案一致性已复核）。</t>
         </is>
       </c>
-      <c r="K19" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>TEM4 p.41；假朋友词典 p.85</t>
         </is>
       </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>APPROVED</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>APPROVED</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>FF4PROD-T1-017</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>FF4PROD-T1-013</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>LEXI_BRIDGE_FF4-0068</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
         <is>
           <t>geste</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>geste</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>语言、用语</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>港口</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>手势；动作；行为</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>细节; 详细</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>笑话</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>怜悯; 仁慈</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="J20" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>法语词：geste；易混英文词：jest。
 TEM4 前 2–3 义项：手势；动作；行为。
@@ -1955,69 +1670,69 @@
 生产审查：APPROVED（核心义完全不重合、词性、选项角色与答案一致性已复核）。</t>
         </is>
       </c>
-      <c r="K20" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>TEM4 p.54；假朋友词典 p.90</t>
         </is>
       </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>APPROVED</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>APPROVED</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>FF4PROD-T1-018</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>FF4PROD-T1-014</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>LEXI_BRIDGE_FF4-0184</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
         <is>
           <t>hardi</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>hardi</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>可携带的; 便携式的</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="E17" s="2" t="inlineStr">
         <is>
           <t>大胆的；放肆的、厚脸皮的</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>细的、薄的; 精美的</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>耐心的; 病人</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>耐寒的；健壮的</t>
         </is>
       </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>给人深刻印象的; 巨大的</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
         <is>
           <t>法语词：hardi；易混英文词：hardy。
 TEM4 前 2–3 义项：大胆的；放肆的、厚脸皮的。
@@ -2026,69 +1741,69 @@
 生产审查：APPROVED（核心义完全不重合、词性、选项角色与答案一致性已复核）。</t>
         </is>
       </c>
-      <c r="K21" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>TEM4 p.144；假朋友词典 p.95</t>
         </is>
       </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>APPROVED</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>APPROVED</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>FF4PROD-T1-019</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>FF4PROD-T1-015</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>LEXI_BRIDGE_FF4-0051</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
         <is>
           <t>hâter</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>hâter</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>仇恨</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>使转向; 拍摄（影视）</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>辩驳; 反驳</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>加速；提前；赶紧</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>摆放; 拥有</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>引起; 导致</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="J22" s="2" t="inlineStr">
+      <c r="J18" s="2" t="inlineStr">
         <is>
           <t>法语词：hâter；易混英文词：hate。
 TEM4 前 2–3 义项：加速；提前；赶紧。
@@ -2097,69 +1812,69 @@
 生产审查：APPROVED（核心义完全不重合、词性、选项角色与答案一致性已复核）。</t>
         </is>
       </c>
-      <c r="K22" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>TEM4 p.46；假朋友词典 p.95</t>
         </is>
       </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>APPROVED</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>APPROVED</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>FF4PROD-T1-020</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>FF4PROD-T1-016</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>LEXI_BRIDGE_FF4-0248</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
         <is>
           <t>instance</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>instance</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>诉讼；恳求、迫切要求</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>材料; 方面</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>担保; 保证</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>实例</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>喧哗; 谣传</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>壁炉; 家</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>诉讼；恳求、迫切要求</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
         <is>
           <t>法语词：instance；易混英文词：instance。
 TEM4 前 2–3 义项：诉讼；恳求、迫切要求。
@@ -2168,140 +1883,69 @@
 生产审查：APPROVED（核心义完全不重合、词性、选项角色与答案一致性已复核）。</t>
         </is>
       </c>
-      <c r="K23" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>TEM4 p.192；假朋友词典 p.104</t>
         </is>
       </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>APPROVED</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>APPROVED</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>FF4PROD-T1-021</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>LEXI_BRIDGE_FF4-0325</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>joli</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>joli</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>漂亮的</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>可爱的; 和蔼可亲的</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>助消化的</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>快乐的；愉快的</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>法语词：joli；易混英文词：jolly。
-TEM4 前 2–3 义项：漂亮的。
-英文迁移义：快乐的；愉快的。
-来源：TEM4 p.255；假朋友词典 p.108。
-生产审查：APPROVED（核心义完全不重合、词性、选项角色与答案一致性已复核）。</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>TEM4 p.255；假朋友词典 p.108</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>APPROVED</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>APPROVED</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>FF4PROD-T1-022</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>FF4PROD-T1-017</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>LEXI_BRIDGE_FF4-0431</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
         <is>
           <t>lecteur</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>lecteur</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>理论、原理</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>直行; 直列</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>读者；朗读者</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>烟囱; 壁炉</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>机体; 人体</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>讲师</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="J25" s="2" t="inlineStr">
+      <c r="J20" s="2" t="inlineStr">
         <is>
           <t>法语词：lecteur；易混英文词：lecturer。
 TEM4 前 2–3 义项：读者；朗读者。
@@ -2310,69 +1954,69 @@
 生产审查：APPROVED（核心义完全不重合、词性、选项角色与答案一致性已复核）。</t>
         </is>
       </c>
-      <c r="K25" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>TEM4 p.358；假朋友词典 p.112</t>
         </is>
       </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>APPROVED</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>APPROVED</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>FF4PROD-T1-023</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>FF4PROD-T1-018</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>LEXI_BRIDGE_FF4-0024</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr">
+      <c r="C21" s="2" t="inlineStr">
         <is>
           <t>licencier</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>licencier</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>混淆; 使困惑</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="E21" s="2" t="inlineStr">
         <is>
           <t>许可</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>描绘; 体现、相当于、意味着</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>使融化、使熔格化; 使合并</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
         <is>
           <t>解雇</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>放置; 提出</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
         <is>
           <t>法语词：licencier；易混英文词：license。
 TEM4 前 2–3 义项：解雇。
@@ -2381,69 +2025,69 @@
 生产审查：APPROVED（核心义完全不重合、词性、选项角色与答案一致性已复核）。</t>
         </is>
       </c>
-      <c r="K26" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>TEM4 p.27；假朋友词典 p.113</t>
         </is>
       </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>APPROVED</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>APPROVED</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>FF4PROD-T1-024</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>FF4PROD-T1-019</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>LEXI_BRIDGE_FF4-0085</t>
         </is>
       </c>
-      <c r="C27" s="2" t="inlineStr">
+      <c r="C22" s="2" t="inlineStr">
         <is>
           <t>lier</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>lier</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>使着迷; 吸引</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>捆；绑；结合</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>犯（罪行、错误）; 做（坏事、蠢事）</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>撒谎；躺</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>冒烟; 熏制</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>捆；绑；结合</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>引起; 导致</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
         <is>
           <t>法语词：lier；易混英文词：lie。
 TEM4 前 2–3 义项：捆；绑；结合。
@@ -2452,69 +2096,69 @@
 生产审查：APPROVED（核心义完全不重合、词性、选项角色与答案一致性已复核）。</t>
         </is>
       </c>
-      <c r="K27" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>TEM4 p.63；假朋友词典 p.113</t>
         </is>
       </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>APPROVED</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t>APPROVED</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>FF4PROD-T1-025</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>FF4PROD-T1-020</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>LEXI_BRIDGE_FF4-0219</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
+      <c r="C23" s="2" t="inlineStr">
         <is>
           <t>mince</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>mince</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="E23" s="2" t="inlineStr">
         <is>
           <t>剁碎肉；细小</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>漂亮的</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>命运的; 决定命运的</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>薄的；瘦长的、细的；微薄的、不重要的</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>美好的</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>液态的; 液体</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
         <is>
           <t>法语词：mince；易混英文词：mince。
 TEM4 前 2–3 义项：薄的；瘦长的、细的；微薄的、不重要的。
@@ -2523,9 +2167,364 @@
 生产审查：APPROVED（核心义完全不重合、词性、选项角色与答案一致性已复核）。</t>
         </is>
       </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>TEM4 p.165；假朋友词典 p.123</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>FF4PROD-T1-021</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>LEXI_BRIDGE_FF4-0410</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>quart</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>quart</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>偶然; 机会</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>夸脱</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>四分之一；一刻钟</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>码头; 站台</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>法语词：quart；易混英文词：quart。
+TEM4 前 2–3 义项：四分之一；一刻钟。
+英文迁移义：夸脱。
+来源：TEM4 p.336；假朋友词典 p.156。
+生产审查：APPROVED（核心义完全不重合、词性、选项角色与答案一致性已复核）。</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>TEM4 p.336；假朋友词典 p.156</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>FF4PROD-T1-022</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>LEXI_BRIDGE_FF4-0064</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>rater</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>rater</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>没有做成功；未命中；未赶上</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>评价；比率</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>判处; 谴责</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>推荐; 叮嘱</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>法语词：rater；易混英文词：rate。
+TEM4 前 2–3 义项：没有做成功；未命中；未赶上。
+英文迁移义：评价；比率。
+来源：TEM4 p.53；假朋友词典 p.159。
+生产审查：APPROVED（核心义完全不重合、词性、选项角色与答案一致性已复核）。</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>TEM4 p.53；假朋友词典 p.159</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>FF4PROD-T1-023</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>LEXI_BRIDGE_FF4-0106</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>严重的; 严重的（事故）</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>漂亮的; 别致的</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>有收益的</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>可出租的</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>法语词：rentable；易混英文词：rentable。
+TEM4 前 2–3 义项：有收益的。
+英文迁移义：可出租的。
+来源：TEM4 p.82；假朋友词典 p.164。
+生产审查：APPROVED（核心义完全不重合、词性、选项角色与答案一致性已复核）。</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>TEM4 p.82；假朋友词典 p.164</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>FF4PROD-T1-024</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>LEXI_BRIDGE_FF4-0330</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>ressentir</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>ressentir</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>表示、意味着</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>怨恨</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>感受到；受到影响</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>总结</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>法语词：ressentir；易混英文词：resent。
+TEM4 前 2–3 义项：感受到；受到影响。
+英文迁移义：怨恨。
+来源：TEM4 p.258；假朋友词典 p.166。
+生产审查：APPROVED（核心义完全不重合、词性、选项角色与答案一致性已复核）。</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>TEM4 p.258；假朋友词典 p.166</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>FF4PROD-T1-025</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>LEXI_BRIDGE_FF4-0290</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>récipient</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>récipient</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>容器</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>接受者</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>绳子; 乐器的弦</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>同等的人或物; 同龄、同辈者</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>法语词：récipient；易混英文词：recipient。
+TEM4 前 2–3 义项：容器。
+英文迁移义：接受者。
+来源：TEM4 p.228；假朋友词典 p.160。
+生产审查：APPROVED（核心义完全不重合、词性、选项角色与答案一致性已复核）。</t>
+        </is>
+      </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>TEM4 p.165；假朋友词典 p.123</t>
+          <t>TEM4 p.228；假朋友词典 p.160</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
@@ -2547,37 +2546,37 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>LEXI_BRIDGE_FF4-0235</t>
+          <t>LEXI_BRIDGE_FF4-0124</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>pair</t>
+          <t>scolaire</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>pair</t>
+          <t>scolaire</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>同等的人或物；同龄、同辈者</t>
+          <t>学校的</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>语言、用语</t>
+          <t>著名的; 极好的</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>一对；配对</t>
+          <t>巨大的; 结实的</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>办事处; 职务</t>
+          <t>学者</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -2587,16 +2586,16 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>法语词：pair；易混英文词：pair。
-TEM4 前 2–3 义项：同等的人或物；同龄、同辈者。
-英文迁移义：一对；配对。
-来源：TEM4 p.178；假朋友词典 p.134。
+          <t>法语词：scolaire；易混英文词：scholar。
+TEM4 前 2–3 义项：学校的。
+英文迁移义：学者。
+来源：TEM4 p.94；假朋友词典 p.174。
 生产审查：APPROVED（核心义完全不重合、词性、选项角色与答案一致性已复核）。</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>TEM4 p.178；假朋友词典 p.134</t>
+          <t>TEM4 p.94；假朋友词典 p.174</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
@@ -2618,58 +2617,56 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>LEXI_BRIDGE_FF4-0021</t>
+          <t>LEXI_BRIDGE_FF4-0334</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>peine</t>
+          <t>singe</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>peine</t>
+          <t>singe</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>搁板; 平板电脑</t>
+          <t>烧焦一点</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>洋葱</t>
+          <t>同等的人或物; 同龄、同辈者</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>刑罚；惩罚；辛劳</t>
+          <t>宝藏、宝库</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>身体疼痛</t>
+          <t>猴子</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>法语词：peine；易混英文词：pain。
-TEM4 前 2–3 义项：刑罚；惩罚；辛劳。
-英文迁移义：身体疼痛。
-来源：TEM4 p.21；假朋友词典 p.140。
-生产审查：APPROVED（核心义完全不重合、词性、选项角色与答案一致性已复核）。
-近义表达（原书证据）：valoir le coup —— (14 $ 19) = valoir le coup de。
-迁移干扰（原书证据）：douleur —— …peine (f) Care is needed. Not physical pain (= douleur (f)), but pain, hurt, di。</t>
+          <t>法语词：singe；易混英文词：singe。
+TEM4 前 2–3 义项：猴子。
+英文迁移义：烧焦一点。
+来源：TEM4 p.260；假朋友词典 p.177。
+生产审查：APPROVED（核心义完全不重合、词性、选项角色与答案一致性已复核）。</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>TEM4 p.21；假朋友词典 p.140</t>
+          <t>TEM4 p.260；假朋友词典 p.177</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
@@ -2699,7 +2696,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:M19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -2850,7 +2847,7 @@
 TEM4 前 2–3 义项：注意到；察觉。
 英文迁移义：评论；言论。
 来源：TEM4 p.303；假朋友词典 p.163。
-生产审查：APPROVED（TEM4 原句、近义词、英语迁移义对应词与答案一致性已复核）。
+生产审查：APPROVED（TEM4 完整原句可定位；近义词、英语迁移义对应词及平行语法已逐项复核）。
 近义表达（原书证据）：repérer —— 07+19) =repérer。
 迁移干扰（原书证据）：dire —— …thing. Remarquez que ...: note that ... To remark (often) = dire.。</t>
         </is>
@@ -2866,6 +2863,1087 @@
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>FF4PROD-T2-002</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>LEXI_BRIDGE_FF4-0021</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>peine</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Ça **vaut la peine** d'aller visiter ce musée.</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>vaut le coup</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>fait mal</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>reste possible</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>semble facile</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>法语词：peine；易混英文词：pain。
+TEM4 前 2–3 义项：刑罚；惩罚；辛劳。
+英文迁移义：身体疼痛。
+来源：TEM4 p.21；假朋友词典 p.140。
+生产审查：APPROVED（TEM4 完整原句可定位；近义词、英语迁移义对应词及平行语法已逐项复核）。
+近义表达（原书证据）：valoir le coup —— (14 $ 19) = valoir le coup de。
+迁移干扰（原书证据）：douleur —— …peine (f) Care is needed. Not physical pain (= douleur (f)), but pain, hurt, di。</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>TEM4 p.21；假朋友词典 p.140</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>FF4PROD-T2-003</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>LEXI_BRIDGE_FF4-0304</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>désigner</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Que **désigne** ce mot dans le texte ?</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>signifie</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>dessine</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>prononce</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>efface</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>法语词：désigner；易混英文词：design。
+TEM4 前 2–3 义项：指、指出；意思是；指定。
+英文迁移义：设计。
+来源：TEM4 p.242；假朋友词典 p.61。
+生产审查：APPROVED（TEM4 完整原句可定位；近义词、英语迁移义对应词及平行语法已逐项复核）。
+迁移干扰（原书证据）：dessiner —— …To design = dessiner, créer. désister Oc。</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>TEM4 p.242；假朋友词典 p.61</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>FF4PROD-T2-004</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>LEXI_BRIDGE_FF4-0366</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>supplier</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Je t'en **supplie**.</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>prie</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>fournis</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>parle</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>veux</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>法语词：supplier；易混英文词：supply。
+TEM4 前 2–3 义项：恳求；请求。
+英文迁移义：供应。
+来源：TEM4 p.284；假朋友词典 p.184。
+生产审查：APPROVED（TEM4 完整原句可定位；近义词、英语迁移义对应词及平行语法已逐项复核）。
+迁移干扰（原书证据）：fournir —— …To supply = fournir, approvisionner. su。</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>TEM4 p.284；假朋友词典 p.184</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>FF4PROD-T2-005</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>LEXI_BRIDGE_FF4-0195</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>tromper</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Sa vue le **trompe** souvent.</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>induit en erreur</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>surpasse</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>protège</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>rassure</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>法语词：tromper；易混英文词：trump。
+TEM4 前 2–3 义项：欺骗；弄错。
+英文迁移义：王牌；胜过。
+来源：TEM4 p.151；假朋友词典 p.193。
+生产审查：APPROVED（TEM4 完整原句可定位；近义词、英语迁移义对应词及平行语法已逐项复核）。
+迁移干扰（原书证据）：atout —— …thing abroad. Also an elephant's trunk. Trump = atout (m).。</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>TEM4 p.151；假朋友词典 p.193</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>FF4PROD-T2-006</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>LEXI_BRIDGE_FF4-0286</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>coin</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Il habite au **coin** de la rue.</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>angle</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>pièce</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>centre</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>sommet</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>法语词：coin；易混英文词：coin。
+TEM4 前 2–3 义项：角落、隅；一小块、一隅之地。
+英文迁移义：硬币。
+来源：TEM4 p.223；假朋友词典 p.39。
+生产审查：APPROVED（基于可定位 TEM4 原搭配补充最小语境；近义词、迁移词和句法已逐项复核）。
+证据等级：基于 TEM4 原搭配“au coin de la rue”补充最小语境，并非逐字原句。</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>TEM4 p.223；假朋友词典 p.39</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>FF4PROD-T2-007</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>LEXI_BRIDGE_FF4-0233</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>convenir</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Cette date me **convient**.</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>va</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>réunit</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>surprend</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>retarde</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>法语词：convenir；易混英文词：convene。
+TEM4 前 2–3 义项：适合、使中意；约定；适合的。
+英文迁移义：召集。
+来源：TEM4 p.177；假朋友词典 p.47。
+生产审查：APPROVED（基于可定位 TEM4 原搭配补充最小语境；近义词、迁移词和句法已逐项复核）。
+证据等级：基于 TEM4 原搭配“convenir à”补充最小语境，并非逐字原句。</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>TEM4 p.177；假朋友词典 p.47</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>FF4PROD-T2-008</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>LEXI_BRIDGE_FF4-0327</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>don</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Elle a un **don** pour la musique.</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>talent</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>seigneur</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>doute</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>goût</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>法语词：don；易混英文词：don。
+TEM4 前 2–3 义项：捐赠；天赋。
+英文迁移义：先生。
+来源：TEM4 p.256；假朋友词典 p.66。
+生产审查：APPROVED（基于可定位 TEM4 原搭配补充最小语境；近义词、迁移词和句法已逐项复核）。
+证据等级：基于 TEM4 原搭配“avoir un don pour la musique”补充最小语境，并非逐字原句。</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>TEM4 p.256；假朋友词典 p.66</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>FF4PROD-T2-009</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>LEXI_BRIDGE_FF4-0325</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>joli</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>C'est une **jolie** petite fille.</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>belle</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>joyeuse</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>timide</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>grande</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>法语词：joli；易混英文词：jolly。
+TEM4 前 2–3 义项：漂亮的。
+英文迁移义：快乐的；愉快的。
+来源：TEM4 p.255；假朋友词典 p.108。
+生产审查：APPROVED（基于可定位 TEM4 原搭配补充最小语境；近义词、迁移词和句法已逐项复核）。
+证据等级：基于 TEM4 原搭配“jolie petite fille”补充最小语境，并非逐字原句。</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>TEM4 p.255；假朋友词典 p.108</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>FF4PROD-T2-010</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>LEXI_BRIDGE_FF4-0235</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>pair</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Cet artiste est sans **pair**.</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>égal</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>paire</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>public</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>avenir</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>法语词：pair；易混英文词：pair。
+TEM4 前 2–3 义项：同等的人或物；同龄、同辈者。
+英文迁移义：一对；配对。
+来源：TEM4 p.178；假朋友词典 p.134。
+生产审查：APPROVED（基于可定位 TEM4 原搭配补充最小语境；近义词、迁移词和句法已逐项复核）。
+证据等级：基于 TEM4 原搭配“sans pair”补充最小语境，并非逐字原句。</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>TEM4 p.178；假朋友词典 p.134</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>FF4PROD-T2-011</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>LEXI_BRIDGE_FF4-0176</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>province</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Ils ont acheté une maison en **province**.</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>région</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>Provence</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>banlieue</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>montagne</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>法语词：province；易混英文词：Provence。
+TEM4 前 2–3 义项：省；外省（法国人指巴黎以外的地方）。
+英文迁移义：普罗旺斯。
+来源：TEM4 p.137；假朋友词典 p.154。
+生产审查：APPROVED（基于可定位 TEM4 原搭配补充最小语境；近义词、迁移词和句法已逐项复核）。
+证据等级：基于 TEM4 原搭配“acheter une maison en province”补充最小语境，并非逐字原句。</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>TEM4 p.137；假朋友词典 p.154</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>FF4PROD-T2-012</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>LEXI_BRIDGE_FF4-0076</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>recette</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>Il cherche une **recette** pour réussir.</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>méthode</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>reçu</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>question</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>chance</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>法语词：recette；易混英文词：receipt。
+TEM4 前 2–3 义项：收入；烹饪法；秘诀。
+英文迁移义：收据。
+来源：TEM4 p.60；假朋友词典 p.160。
+生产审查：APPROVED（基于可定位 TEM4 原搭配补充最小语境；近义词、迁移词和句法已逐项复核）。
+证据等级：基于 TEM4 原搭配“recette pour réussir”补充最小语境，并非逐字原句。</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>TEM4 p.60；假朋友词典 p.160</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>FF4PROD-T2-013</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>LEXI_BRIDGE_FF4-0315</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>reporter</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Ils ont **reporté** la cérémonie.</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>remis</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>rapporté</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>annoncé</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>préparé</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>法语词：reporter；易混英文词：report。
+TEM4 前 2–3 义项：送回、送还；推迟。
+英文迁移义：报道；报告。
+来源：TEM4 p.249；假朋友词典 p.165。
+生产审查：APPROVED（基于可定位 TEM4 原搭配补充最小语境；近义词、迁移词和句法已逐项复核）。
+证据等级：基于 TEM4 原搭配“reporter la cérémonie = remettre”补充最小语境，并非逐字原句。</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>TEM4 p.249；假朋友词典 p.165</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>FF4PROD-T2-014</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>LEXI_BRIDGE_FF4-0149</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>résumer</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>Elle **résume** une histoire.</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>synthétise</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>reprend</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>invente</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>traduit</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>法语词：résumer；易混英文词：resume。
+TEM4 前 2–3 义项：总结。
+英文迁移义：简历；继续。
+来源：TEM4 p.111；假朋友词典 p.166。
+生产审查：APPROVED（基于可定位 TEM4 原搭配补充最小语境；近义词、迁移词和句法已逐项复核）。
+证据等级：基于 TEM4 原搭配“résumer une histoire”补充最小语境，并非逐字原句。</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>TEM4 p.111；假朋友词典 p.166</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>FF4PROD-T2-015</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>LEXI_BRIDGE_FF4-0125</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>sort</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>Il est maître de son **sort**.</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>destin</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>secret</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>choix</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>法语词：sort；易混英文词：sort。
+TEM4 前 2–3 义项：命运；遭遇；运气。
+英文迁移义：种类；分类。
+来源：TEM4 p.96；假朋友词典 p.179。
+生产审查：APPROVED（基于可定位 TEM4 原搭配补充最小语境；近义词、迁移词和句法已逐项复核）。
+证据等级：基于 TEM4 原搭配“être maître du sort de quelqu'un”补充最小语境，并非逐字原句。</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>TEM4 p.96；假朋友词典 p.179</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>FF4PROD-T2-016</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>LEXI_BRIDGE_FF4-0167</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>toile</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>Il admire une **toile** de Cézanne.</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>tableau</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>labeur</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>sculpture</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>photo</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>法语词：toile；易混英文词：toil。
+TEM4 前 2–3 义项：布；织物；画布上的画。
+英文迁移义：辛劳。
+来源：TEM4 p.129；假朋友词典 p.189。
+生产审查：APPROVED（基于可定位 TEM4 原搭配补充最小语境；近义词、迁移词和句法已逐项复核）。
+证据等级：基于 TEM4 原搭配“toile de Cézanne”补充最小语境，并非逐字原句。</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>TEM4 p.129；假朋友词典 p.189</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
         <is>
           <t>APPROVED</t>
         </is>
@@ -2887,7 +3965,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M30"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -2915,7 +3993,7 @@
     <row r="2" ht="36" customHeight="1">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>题型三｜严格按 0811 文档使用英文迁移义，全部答案自然为 F。</t>
+          <t>题型三｜假朋友题答案为 F，并穿插 10 道英法同形同义 Vrai 控制题。</t>
         </is>
       </c>
     </row>
@@ -2994,17 +4072,17 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>LEXI_BRIDGE_FF4-0122</t>
+          <t>LEXI_BRIDGE_FF4-0009</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>car</t>
+          <t>surnommer</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>car = 汽车</t>
+          <t>surnommer = 给姓氏；姓氏</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -3025,1665 +4103,1348 @@
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>法语词：surnommer；易混英文词：surname。
+TEM4 前 2–3 义项：给…起外号。
+英文迁移义：给姓氏；姓氏。
+来源：TEM4 p.13；假朋友词典 p.185。
+生产审查：APPROVED（假朋友英语迁移义命题，标准答案为 F）。</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>TEM4 p.13；假朋友词典 p.185</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>FF4PROD-T3-002</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>LEXI_BRIDGE_FF4-0273</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>encore</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>encore = 返场</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Vrai（正确）</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Faux（错误）</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="n"/>
+      <c r="H5" s="2" t="n"/>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>法语词：encore；易混英文词：encore。
+TEM4 前 2–3 义项：还、尚、仍；又、再。
+英文迁移义：返场。
+来源：TEM4 p.208；假朋友词典 p.71。
+生产审查：APPROVED（假朋友英语迁移义命题，标准答案为 F）。</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>TEM4 p.208；假朋友词典 p.71</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>FF4PROD-T3-003</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>LEXI_BRIDGE_FF4-0034</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>science</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>science = 科学</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Vrai（正确）</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Faux（错误）</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="n"/>
+      <c r="H6" s="2" t="n"/>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>法语词：science；易混英文词：science。
+TEM4 前 2–3 义项：科学；某一门学科。
+英文迁移义：科学。
+来源：TEM4 p.36；假朋友词典 p.174。
+生产审查：APPROVED（英法同形同义 Vrai 控制题；用于降低全 F 反应定势）。</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>TEM4 p.36；假朋友词典 p.174</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>FF4PROD-T3-004</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>LEXI_BRIDGE_FF4-0022</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>verger</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>verger = 执达员</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Vrai（正确）</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>Faux（错误）</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="n"/>
+      <c r="H7" s="2" t="n"/>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>法语词：verger；易混英文词：verger。
+TEM4 前 2–3 义项：果园。
+英文迁移义：执达员。
+来源：TEM4 p.22；假朋友词典 p.198。
+生产审查：APPROVED（假朋友英语迁移义命题，标准答案为 F）。</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>TEM4 p.22；假朋友词典 p.198</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>FF4PROD-T3-005</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>LEXI_BRIDGE_FF4-0039</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>villa</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>villa = 别墅</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Vrai（正确）</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Faux（错误）</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="n"/>
+      <c r="H8" s="2" t="n"/>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>法语词：villa；易混英文词：villa。
+TEM4 前 2–3 义项：别墅。
+英文迁移义：别墅。
+来源：TEM4 p.41；假朋友词典 p.199。
+生产审查：APPROVED（英法同形同义 Vrai 控制题；用于降低全 F 反应定势）。</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>TEM4 p.41；假朋友词典 p.199</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>FF4PROD-T3-006</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>LEXI_BRIDGE_FF4-0395</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>solde</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>solde = 已售的</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>Vrai（正确）</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>Faux（错误）</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="n"/>
+      <c r="H9" s="2" t="n"/>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>法语词：solde；易混英文词：sold。
+TEM4 前 2–3 义项：余额；清仓存货；军饷。
+英文迁移义：已售的。
+来源：TEM4 p.322；假朋友词典 p.179。
+生产审查：APPROVED（假朋友英语迁移义命题，标准答案为 F）。</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>TEM4 p.322；假朋友词典 p.179</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>FF4PROD-T3-007</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>LEXI_BRIDGE_FF4-0046</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>radio</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>radio = 收音机</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>Vrai（正确）</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>Faux（错误）</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="n"/>
+      <c r="H10" s="2" t="n"/>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>法语词：radio；易混英文词：radio。
+TEM4 前 2–3 义项：广播；收音机；射线透视检查。
+英文迁移义：收音机；无线电。
+来源：TEM4 p.43；假朋友词典 p.157。
+生产审查：APPROVED（英法同形同义 Vrai 控制题；用于降低全 F 反应定势）。</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>TEM4 p.43；假朋友词典 p.157</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>FF4PROD-T3-008</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>LEXI_BRIDGE_FF4-0199</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>vaisselle</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>vaisselle = 容器；船</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>Vrai（正确）</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>Faux（错误）</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="n"/>
+      <c r="H11" s="2" t="n"/>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>法语词：vaisselle；易混英文词：vessel。
+TEM4 前 2–3 义项：餐具；需洗刷的餐具。
+英文迁移义：容器；船。
+来源：TEM4 p.156；假朋友词典 p.196。
+生产审查：APPROVED（假朋友英语迁移义命题，标准答案为 F）。</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>TEM4 p.156；假朋友词典 p.196</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>FF4PROD-T3-009</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>LEXI_BRIDGE_FF4-0187</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>flatter</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>flatter = 奉承</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Vrai（正确）</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>Faux（错误）</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="n"/>
+      <c r="H12" s="2" t="n"/>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>法语词：flatter；易混英文词：flatter。
+TEM4 前 2–3 义项：奉承。
+英文迁移义：奉承。
+来源：TEM4 p.147；假朋友词典 p.82。
+生产审查：APPROVED（英法同形同义 Vrai 控制题；用于降低全 F 反应定势）。</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>TEM4 p.147；假朋友词典 p.82</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>FF4PROD-T3-010</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>LEXI_BRIDGE_FF4-0436</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>tirer</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>tirer = 轮胎；疲倦</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>Vrai（正确）</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>Faux（错误）</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="n"/>
+      <c r="H13" s="2" t="n"/>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>法语词：tirer；易混英文词：tire。
+TEM4 前 2–3 义项：拉；抽取；射击。
+英文迁移义：轮胎；疲倦。
+来源：TEM4 p.360；假朋友词典 p.189。
+生产审查：APPROVED（假朋友英语迁移义命题，标准答案为 F）。</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>TEM4 p.360；假朋友词典 p.189</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>FF4PROD-T3-011</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>LEXI_BRIDGE_FF4-0255</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>dragon</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>dragon = 龙</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Vrai（正确）</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>Faux（错误）</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="n"/>
+      <c r="H14" s="2" t="n"/>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>法语词：dragon；易混英文词：dragon。
+TEM4 前 2–3 义项：龙。
+英文迁移义：龙。
+来源：TEM4 p.196；假朋友词典 p.67。
+生产审查：APPROVED（英法同形同义 Vrai 控制题；用于降低全 F 反应定势）。</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>TEM4 p.196；假朋友词典 p.67</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>FF4PROD-T3-012</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>LEXI_BRIDGE_FF4-0050</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>trier</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>trier = 尝试</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>Vrai（正确）</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>Faux（错误）</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="n"/>
+      <c r="H15" s="2" t="n"/>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>法语词：trier；易混英文词：try。
+TEM4 前 2–3 义项：挑选；分拣；分类。
+英文迁移义：尝试。
+来源：TEM4 p.44；假朋友词典 p.192。
+生产审查：APPROVED（假朋友英语迁移义命题，标准答案为 F）。</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>TEM4 p.44；假朋友词典 p.192</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>FF4PROD-T3-013</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>LEXI_BRIDGE_FF4-0281</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>opinion</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>opinion = 意见</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>Vrai（正确）</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>Faux（错误）</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="n"/>
+      <c r="H16" s="2" t="n"/>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>法语词：opinion；易混英文词：opinion。
+TEM4 前 2–3 义项：意见；舆论。
+英文迁移义：意见。
+来源：TEM4 p.220；假朋友词典 p.132。
+生产审查：APPROVED（英法同形同义 Vrai 控制题；用于降低全 F 反应定势）。</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>TEM4 p.220；假朋友词典 p.132</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>FF4PROD-T3-014</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>LEXI_BRIDGE_FF4-0122</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>car</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>car = 汽车</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>Vrai（正确）</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>Faux（错误）</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="n"/>
+      <c r="H17" s="2" t="n"/>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
         <is>
           <t>法语词：car；易混英文词：car。
 TEM4 前 2–3 义项：因为。
 英文迁移义：汽车。
 来源：TEM4 p.92；假朋友词典 p.31。
-生产审查：APPROVED（严格使用英语迁移义命题，标准答案为 F）。</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
+生产审查：APPROVED（假朋友英语迁移义命题，标准答案为 F）。</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>TEM4 p.92；假朋友词典 p.31</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>APPROVED</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>APPROVED</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>FF4PROD-T3-002</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>LEXI_BRIDGE_FF4-0273</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>encore</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>encore = 返场</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>FF4PROD-T3-015</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>LEXI_BRIDGE_FF4-0349</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>site</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>site = 网站</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>Vrai（正确）</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>Faux（错误）</t>
         </is>
       </c>
-      <c r="G5" s="2" t="n"/>
-      <c r="H5" s="2" t="n"/>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="G18" s="2" t="n"/>
+      <c r="H18" s="2" t="n"/>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>法语词：site；易混英文词：site。
+TEM4 前 2–3 义项：地点；网站。
+英文迁移义：地点；网站。
+来源：TEM4 p.267；假朋友词典 p.177。
+生产审查：APPROVED（英法同形同义 Vrai 控制题；用于降低全 F 反应定势）。</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>TEM4 p.267；假朋友词典 p.177</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>FF4PROD-T3-016</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>LEXI_BRIDGE_FF4-0102</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>stage</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>stage = 舞台；阶段</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>Vrai（正确）</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>Faux（错误）</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="n"/>
+      <c r="H19" s="2" t="n"/>
+      <c r="I19" s="2" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>法语词：encore；易混英文词：encore。
-TEM4 前 2–3 义项：还、尚、仍；又、再。
-英文迁移义：返场。
-来源：TEM4 p.208；假朋友词典 p.71。
-生产审查：APPROVED（严格使用英语迁移义命题，标准答案为 F）。</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>TEM4 p.208；假朋友词典 p.71</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>APPROVED</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>APPROVED</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>FF4PROD-T3-003</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>法语词：stage；易混英文词：stage。
+TEM4 前 2–3 义项：实习期；培训期。
+英文迁移义：舞台；阶段。
+来源：TEM4 p.77；假朋友词典 p.181。
+生产审查：APPROVED（假朋友英语迁移义命题，标准答案为 F）。</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>TEM4 p.77；假朋友词典 p.181</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>FF4PROD-T3-017</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>LEXI_BRIDGE_FF4-0353</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>standard = 标准</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>Vrai（正确）</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>Faux（错误）</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="n"/>
+      <c r="H20" s="2" t="n"/>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>法语词：standard；易混英文词：standard。
+TEM4 前 2–3 义项：标准。
+英文迁移义：标准。
+来源：TEM4 p.270；假朋友词典 p.181。
+生产审查：APPROVED（英法同形同义 Vrai 控制题；用于降低全 F 反应定势）。</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>TEM4 p.270；假朋友词典 p.181</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>FF4PROD-T3-018</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>LEXI_BRIDGE_FF4-0295</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>somme</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>somme = 一些</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>Vrai（正确）</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>Faux（错误）</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="n"/>
+      <c r="H21" s="2" t="n"/>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>法语词：somme；易混英文词：some。
+TEM4 前 2–3 义项：金额、款项；总量。
+英文迁移义：一些。
+来源：TEM4 p.230；假朋友词典 p.179。
+生产审查：APPROVED（假朋友英语迁移义命题，标准答案为 F）。</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>TEM4 p.230；假朋友词典 p.179</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>FF4PROD-T3-019</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>LEXI_BRIDGE_FF4-0380</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>contact</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>contact = 联系</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>Vrai（正确）</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>Faux（错误）</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="n"/>
+      <c r="H22" s="2" t="n"/>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>法语词：contact；易混英文词：contact。
+TEM4 前 2–3 义项：联系；接触。
+英文迁移义：联系。
+来源：TEM4 p.303；假朋友词典 p.46。
+生产审查：APPROVED（英法同形同义 Vrai 控制题；用于降低全 F 反应定势）。</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>TEM4 p.303；假朋友词典 p.46</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>FF4PROD-T3-020</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>LEXI_BRIDGE_FF4-0057</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>taper</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>taper = 胶带；录制</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>Vrai（正确）</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>Faux（错误）</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="n"/>
+      <c r="H23" s="2" t="n"/>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>法语词：taper；易混英文词：tape。
+TEM4 前 2–3 义项：打字；拍打；敲击。
+英文迁移义：胶带；录制。
+来源：TEM4 p.49；假朋友词典 p.187。
+生产审查：APPROVED（假朋友英语迁移义命题，标准答案为 F）。</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>TEM4 p.49；假朋友词典 p.187</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>FF4PROD-T3-021</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>LEXI_BRIDGE_FF4-0432</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>ski</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>ski = 滑雪；滑雪板</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>Vrai（正确）</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>Faux（错误）</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="n"/>
+      <c r="H24" s="2" t="n"/>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>法语词：ski；易混英文词：ski。
+TEM4 前 2–3 义项：滑雪；滑雪板。
+英文迁移义：滑雪；滑雪板。
+来源：TEM4 p.358；假朋友词典 p.178。
+生产审查：APPROVED（英法同形同义 Vrai 控制题；用于降低全 F 反应定势）。</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>TEM4 p.358；假朋友词典 p.178</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>FF4PROD-T3-022</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>LEXI_BRIDGE_FF4-0266</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C25" s="2" t="inlineStr">
         <is>
           <t>or</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>or = 或者</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E25" s="2" t="inlineStr">
         <is>
           <t>Vrai（正确）</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F25" s="2" t="inlineStr">
         <is>
           <t>Faux（错误）</t>
         </is>
       </c>
-      <c r="G6" s="2" t="n"/>
-      <c r="H6" s="2" t="n"/>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="G25" s="2" t="n"/>
+      <c r="H25" s="2" t="n"/>
+      <c r="I25" s="2" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr">
+      <c r="J25" s="2" t="inlineStr">
         <is>
           <t>法语词：or；易混英文词：or。
 TEM4 前 2–3 义项：然而。
 英文迁移义：或者。
 来源：TEM4 p.205；假朋友词典 p.133。
-生产审查：APPROVED（严格使用英语迁移义命题，标准答案为 F）。</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
+生产审查：APPROVED（假朋友英语迁移义命题，标准答案为 F）。</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
         <is>
           <t>TEM4 p.205；假朋友词典 p.133</t>
         </is>
       </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>APPROVED</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>APPROVED</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>FF4PROD-T3-004</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>LEXI_BRIDGE_FF4-0176</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>province</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>province = 普罗旺斯</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>Vrai（正确）</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>Faux（错误）</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="n"/>
-      <c r="H7" s="2" t="n"/>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>法语词：province；易混英文词：Provence。
-TEM4 前 2–3 义项：省；外省（法国人指巴黎以外的地方）。
-英文迁移义：普罗旺斯。
-来源：TEM4 p.137；假朋友词典 p.154。
-生产审查：APPROVED（严格使用英语迁移义命题，标准答案为 F）。</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>TEM4 p.137；假朋友词典 p.154</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>APPROVED</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>APPROVED</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>FF4PROD-T3-005</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>LEXI_BRIDGE_FF4-0410</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>quart</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>quart = 夸脱</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>Vrai（正确）</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>Faux（错误）</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="n"/>
-      <c r="H8" s="2" t="n"/>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>法语词：quart；易混英文词：quart。
-TEM4 前 2–3 义项：四分之一；一刻钟。
-英文迁移义：夸脱。
-来源：TEM4 p.336；假朋友词典 p.156。
-生产审查：APPROVED（严格使用英语迁移义命题，标准答案为 F）。</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>TEM4 p.336；假朋友词典 p.156</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>APPROVED</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>APPROVED</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>FF4PROD-T3-006</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>LEXI_BRIDGE_FF4-0064</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>rater</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>rater = 评价；比率</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>Vrai（正确）</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>Faux（错误）</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="n"/>
-      <c r="H9" s="2" t="n"/>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>法语词：rater；易混英文词：rate。
-TEM4 前 2–3 义项：没有做成功；未命中；未赶上。
-英文迁移义：评价；比率。
-来源：TEM4 p.53；假朋友词典 p.159。
-生产审查：APPROVED（严格使用英语迁移义命题，标准答案为 F）。</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>TEM4 p.53；假朋友词典 p.159</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>APPROVED</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>APPROVED</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>FF4PROD-T3-007</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>LEXI_BRIDGE_FF4-0076</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>recette</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>recette = 收据</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>Vrai（正确）</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>Faux（错误）</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="n"/>
-      <c r="H10" s="2" t="n"/>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>法语词：recette；易混英文词：receipt。
-TEM4 前 2–3 义项：收入；烹饪法；秘诀。
-英文迁移义：收据。
-来源：TEM4 p.60；假朋友词典 p.160。
-生产审查：APPROVED（严格使用英语迁移义命题，标准答案为 F）。</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>TEM4 p.60；假朋友词典 p.160</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>APPROVED</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>APPROVED</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>FF4PROD-T3-008</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>LEXI_BRIDGE_FF4-0106</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>rentable</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>rentable = 可出租的</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>Vrai（正确）</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>Faux（错误）</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="n"/>
-      <c r="H11" s="2" t="n"/>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>法语词：rentable；易混英文词：rentable。
-TEM4 前 2–3 义项：有收益的。
-英文迁移义：可出租的。
-来源：TEM4 p.82；假朋友词典 p.164。
-生产审查：APPROVED（严格使用英语迁移义命题，标准答案为 F）。</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>TEM4 p.82；假朋友词典 p.164</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>APPROVED</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>APPROVED</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>FF4PROD-T3-009</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>LEXI_BRIDGE_FF4-0315</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>reporter</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>reporter = 报道；报告</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>Vrai（正确）</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>Faux（错误）</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="n"/>
-      <c r="H12" s="2" t="n"/>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>法语词：reporter；易混英文词：report。
-TEM4 前 2–3 义项：送回、送还；推迟。
-英文迁移义：报道；报告。
-来源：TEM4 p.249；假朋友词典 p.165。
-生产审查：APPROVED（严格使用英语迁移义命题，标准答案为 F）。</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>TEM4 p.249；假朋友词典 p.165</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>APPROVED</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>APPROVED</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>FF4PROD-T3-010</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>LEXI_BRIDGE_FF4-0330</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>ressentir</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>ressentir = 怨恨</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>Vrai（正确）</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>Faux（错误）</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="n"/>
-      <c r="H13" s="2" t="n"/>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>法语词：ressentir；易混英文词：resent。
-TEM4 前 2–3 义项：感受到；受到影响。
-英文迁移义：怨恨。
-来源：TEM4 p.258；假朋友词典 p.166。
-生产审查：APPROVED（严格使用英语迁移义命题，标准答案为 F）。</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>TEM4 p.258；假朋友词典 p.166</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>APPROVED</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>APPROVED</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>FF4PROD-T3-011</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>LEXI_BRIDGE_FF4-0290</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>récipient</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>récipient = 接受者</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>Vrai（正确）</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>Faux（错误）</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="n"/>
-      <c r="H14" s="2" t="n"/>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>法语词：récipient；易混英文词：recipient。
-TEM4 前 2–3 义项：容器。
-英文迁移义：接受者。
-来源：TEM4 p.228；假朋友词典 p.160。
-生产审查：APPROVED（严格使用英语迁移义命题，标准答案为 F）。</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>TEM4 p.228；假朋友词典 p.160</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>APPROVED</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>APPROVED</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>FF4PROD-T3-012</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>LEXI_BRIDGE_FF4-0149</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>résumer</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>résumer = 简历；继续</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>Vrai（正确）</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>Faux（错误）</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="n"/>
-      <c r="H15" s="2" t="n"/>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>法语词：résumer；易混英文词：resume。
-TEM4 前 2–3 义项：总结。
-英文迁移义：简历；继续。
-来源：TEM4 p.111；假朋友词典 p.166。
-生产审查：APPROVED（严格使用英语迁移义命题，标准答案为 F）。</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>TEM4 p.111；假朋友词典 p.166</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>APPROVED</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>APPROVED</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>FF4PROD-T3-013</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>LEXI_BRIDGE_FF4-0124</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>scolaire</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>scolaire = 学者</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>Vrai（正确）</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>Faux（错误）</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="n"/>
-      <c r="H16" s="2" t="n"/>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>法语词：scolaire；易混英文词：scholar。
-TEM4 前 2–3 义项：学校的。
-英文迁移义：学者。
-来源：TEM4 p.94；假朋友词典 p.174。
-生产审查：APPROVED（严格使用英语迁移义命题，标准答案为 F）。</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>TEM4 p.94；假朋友词典 p.174</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>APPROVED</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>APPROVED</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>FF4PROD-T3-014</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>LEXI_BRIDGE_FF4-0334</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>singe</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>singe = 烧焦一点</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>Vrai（正确）</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>Faux（错误）</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="n"/>
-      <c r="H17" s="2" t="n"/>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>法语词：singe；易混英文词：singe。
-TEM4 前 2–3 义项：猴子。
-英文迁移义：烧焦一点。
-来源：TEM4 p.260；假朋友词典 p.177。
-生产审查：APPROVED（严格使用英语迁移义命题，标准答案为 F）。</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>TEM4 p.260；假朋友词典 p.177</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>APPROVED</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>APPROVED</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>FF4PROD-T3-015</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>LEXI_BRIDGE_FF4-0395</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>solde</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>solde = 已售的</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>Vrai（正确）</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>Faux（错误）</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="n"/>
-      <c r="H18" s="2" t="n"/>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>法语词：solde；易混英文词：sold。
-TEM4 前 2–3 义项：余额；清仓存货；军饷。
-英文迁移义：已售的。
-来源：TEM4 p.322；假朋友词典 p.179。
-生产审查：APPROVED（严格使用英语迁移义命题，标准答案为 F）。</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>TEM4 p.322；假朋友词典 p.179</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>APPROVED</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>APPROVED</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>FF4PROD-T3-016</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>LEXI_BRIDGE_FF4-0295</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>somme</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>somme = 一些</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>Vrai（正确）</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>Faux（错误）</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="n"/>
-      <c r="H19" s="2" t="n"/>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>法语词：somme；易混英文词：some。
-TEM4 前 2–3 义项：金额、款项；总量。
-英文迁移义：一些。
-来源：TEM4 p.230；假朋友词典 p.179。
-生产审查：APPROVED（严格使用英语迁移义命题，标准答案为 F）。</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>TEM4 p.230；假朋友词典 p.179</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>APPROVED</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>APPROVED</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>FF4PROD-T3-017</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>LEXI_BRIDGE_FF4-0125</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>sort</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>sort = 种类；分类</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>Vrai（正确）</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>Faux（错误）</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="n"/>
-      <c r="H20" s="2" t="n"/>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>法语词：sort；易混英文词：sort。
-TEM4 前 2–3 义项：命运；遭遇；运气。
-英文迁移义：种类；分类。
-来源：TEM4 p.96；假朋友词典 p.179。
-生产审查：APPROVED（严格使用英语迁移义命题，标准答案为 F）。</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>TEM4 p.96；假朋友词典 p.179</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>APPROVED</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>APPROVED</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>FF4PROD-T3-018</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>LEXI_BRIDGE_FF4-0102</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>stage</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>stage = 舞台；阶段</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>Vrai（正确）</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>Faux（错误）</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="n"/>
-      <c r="H21" s="2" t="n"/>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>法语词：stage；易混英文词：stage。
-TEM4 前 2–3 义项：实习期；培训期。
-英文迁移义：舞台；阶段。
-来源：TEM4 p.77；假朋友词典 p.181。
-生产审查：APPROVED（严格使用英语迁移义命题，标准答案为 F）。</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>TEM4 p.77；假朋友词典 p.181</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>APPROVED</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>APPROVED</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>FF4PROD-T3-019</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>LEXI_BRIDGE_FF4-0366</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>supplier</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>supplier = 供应</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>Vrai（正确）</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>Faux（错误）</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="n"/>
-      <c r="H22" s="2" t="n"/>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>法语词：supplier；易混英文词：supply。
-TEM4 前 2–3 义项：恳求；请求。
-英文迁移义：供应。
-来源：TEM4 p.284；假朋友词典 p.184。
-生产审查：APPROVED（严格使用英语迁移义命题，标准答案为 F）。
-迁移干扰（原书证据）：fournir —— …To supply = fournir, approvisionner. su。</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>TEM4 p.284；假朋友词典 p.184</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>APPROVED</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>APPROVED</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>FF4PROD-T3-020</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>LEXI_BRIDGE_FF4-0009</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>surnommer</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>surnommer = 给姓氏；姓氏</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>Vrai（正确）</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>Faux（错误）</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="n"/>
-      <c r="H23" s="2" t="n"/>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>法语词：surnommer；易混英文词：surname。
-TEM4 前 2–3 义项：给…起外号。
-英文迁移义：给姓氏；姓氏。
-来源：TEM4 p.13；假朋友词典 p.185。
-生产审查：APPROVED（严格使用英语迁移义命题，标准答案为 F）。</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>TEM4 p.13；假朋友词典 p.185</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>APPROVED</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>APPROVED</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>FF4PROD-T3-021</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>LEXI_BRIDGE_FF4-0057</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>taper</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>taper = 胶带；录制</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>Vrai（正确）</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>Faux（错误）</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="n"/>
-      <c r="H24" s="2" t="n"/>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>法语词：taper；易混英文词：tape。
-TEM4 前 2–3 义项：打字；拍打；敲击。
-英文迁移义：胶带；录制。
-来源：TEM4 p.49；假朋友词典 p.187。
-生产审查：APPROVED（严格使用英语迁移义命题，标准答案为 F）。</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>TEM4 p.49；假朋友词典 p.187</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>APPROVED</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>APPROVED</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>FF4PROD-T3-022</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>LEXI_BRIDGE_FF4-0436</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>tirer</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>tirer = 轮胎；疲倦</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>Vrai（正确）</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>Faux（错误）</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="n"/>
-      <c r="H25" s="2" t="n"/>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>法语词：tirer；易混英文词：tire。
-TEM4 前 2–3 义项：拉；抽取；射击。
-英文迁移义：轮胎；疲倦。
-来源：TEM4 p.360；假朋友词典 p.189。
-生产审查：APPROVED（严格使用英语迁移义命题，标准答案为 F）。</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>TEM4 p.360；假朋友词典 p.189</t>
-        </is>
-      </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
           <t>APPROVED</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>APPROVED</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>FF4PROD-T3-023</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>LEXI_BRIDGE_FF4-0167</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>toile</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>toile = 辛劳</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>Vrai（正确）</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>Faux（错误）</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="n"/>
-      <c r="H26" s="2" t="n"/>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>法语词：toile；易混英文词：toil。
-TEM4 前 2–3 义项：布；织物；画布上的画。
-英文迁移义：辛劳。
-来源：TEM4 p.129；假朋友词典 p.189。
-生产审查：APPROVED（严格使用英语迁移义命题，标准答案为 F）。</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>TEM4 p.129；假朋友词典 p.189</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>APPROVED</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>APPROVED</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>FF4PROD-T3-024</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>LEXI_BRIDGE_FF4-0050</t>
-        </is>
-      </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>trier</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>trier = 尝试</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>Vrai（正确）</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>Faux（错误）</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="n"/>
-      <c r="H27" s="2" t="n"/>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>法语词：trier；易混英文词：try。
-TEM4 前 2–3 义项：挑选；分拣；分类。
-英文迁移义：尝试。
-来源：TEM4 p.44；假朋友词典 p.192。
-生产审查：APPROVED（严格使用英语迁移义命题，标准答案为 F）。</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>TEM4 p.44；假朋友词典 p.192</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>APPROVED</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t>APPROVED</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>FF4PROD-T3-025</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>LEXI_BRIDGE_FF4-0195</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>tromper</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>tromper = 王牌；胜过</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>Vrai（正确）</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>Faux（错误）</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="n"/>
-      <c r="H28" s="2" t="n"/>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>法语词：tromper；易混英文词：trump。
-TEM4 前 2–3 义项：欺骗；弄错。
-英文迁移义：王牌；胜过。
-来源：TEM4 p.151；假朋友词典 p.193。
-生产审查：APPROVED（严格使用英语迁移义命题，标准答案为 F）。
-迁移干扰（原书证据）：atout —— …thing abroad. Also an elephant's trunk. Trump = atout (m).。</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>TEM4 p.151；假朋友词典 p.193</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t>APPROVED</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t>APPROVED</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>FF4PROD-T3-026</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>LEXI_BRIDGE_FF4-0199</t>
-        </is>
-      </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>vaisselle</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>vaisselle = 容器；船</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>Vrai（正确）</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>Faux（错误）</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="n"/>
-      <c r="H29" s="2" t="n"/>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>法语词：vaisselle；易混英文词：vessel。
-TEM4 前 2–3 义项：餐具；需洗刷的餐具。
-英文迁移义：容器；船。
-来源：TEM4 p.156；假朋友词典 p.196。
-生产审查：APPROVED（严格使用英语迁移义命题，标准答案为 F）。</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>TEM4 p.156；假朋友词典 p.196</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="inlineStr">
-        <is>
-          <t>APPROVED</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr">
-        <is>
-          <t>APPROVED</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>FF4PROD-T3-027</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>LEXI_BRIDGE_FF4-0022</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>verger</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>verger = 执达员</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>Vrai（正确）</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>Faux（错误）</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="n"/>
-      <c r="H30" s="2" t="n"/>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>法语词：verger；易混英文词：verger。
-TEM4 前 2–3 义项：果园。
-英文迁移义：执达员。
-来源：TEM4 p.22；假朋友词典 p.198。
-生产审查：APPROVED（严格使用英语迁移义命题，标准答案为 F）。</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="inlineStr">
-        <is>
-          <t>TEM4 p.22；假朋友词典 p.198</t>
-        </is>
-      </c>
-      <c r="L30" s="2" t="inlineStr">
-        <is>
-          <t>APPROVED</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="inlineStr">
         <is>
           <t>APPROVED</t>
         </is>
@@ -14467,7 +15228,7 @@
       <c r="C4" s="2" t="inlineStr">
         <is>
           <t>亲爱的同学：
-您好！欢迎参与本次英法词汇认知迁移研究。姓名和联系方式仅用于研究参与确认与必要联络；资料会加密保存，并与正式答题、评分、自动分析和普通结果页面隔离，仅限问卷所有者或管理员在授权场景访问。正式测试共 229 题，预计最多 120 分钟，资料填写时间不计入测试。请勿查阅词典或与他人交流，独立完成作答。</t>
+您好！欢迎参与本次英法词汇认知迁移研究。姓名和联系方式仅用于研究参与确认与必要联络；资料会加密保存，并与正式答题、评分、自动分析和普通结果页面隔离，仅限问卷所有者或管理员在授权场景访问。正式测试共 239 题，预计最多 120 分钟，资料填写时间不计入测试。请勿查阅词典或与他人交流，独立完成作答。</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
